--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4020,8 +4127,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4040,973 +4151,941 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">통영 개타령 — 민요채보-3/통영 개타령.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">통영 개타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" s="13"/>
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" s="13"/>
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="13"/>
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">멍</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="M3" s="13"/>
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="14"/>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">멍</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">멍</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">질</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O4" s="14"/>
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">름</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="15"/>
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">멍</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K5" s="15"/>
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q5" s="15"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K6" s="13"/>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M6" s="13"/>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O6" s="13"/>
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">혀</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">매</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="14"/>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="14"/>
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">짖</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="14"/>
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">짖</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K8" s="15"/>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="N8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O8" s="15"/>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q8" s="15"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="13"/>
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="13"/>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">롱</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="Q9" s="13"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="14"/>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="14"/>
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="G10" s="14"/>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M10" s="14"/>
+      <c r="N10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">검</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="15"/>
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="15"/>
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="15"/>
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="M11" s="15"/>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O11" s="15"/>
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">둥</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="13"/>
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="13"/>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="O12" s="13"/>
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="Q12" s="13"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="14"/>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="14"/>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="14"/>
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="O13" s="14"/>
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="E14" s="15"/>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K14" s="15"/>
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="M14" s="15"/>
+      <c r="N14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O14" s="15"/>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -417,7 +417,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3019,59 +3066,59 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">통영 개타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 姑</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">멍</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가강</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3079,46 +3126,46 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">멍</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -3126,37 +3173,37 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="27"/>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="27"/>
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">만살</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3164,36 +3211,36 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌
 仲</t>
         </is>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="E6" s="29"/>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G6" s="28"/>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -3201,43 +3248,43 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 潢</t>
         </is>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="E7" s="26"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">깨그려오</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">검</t>
         </is>
@@ -3245,34 +3292,34 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑
 仲</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="27"/>
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 姑</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="27"/>
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="G8" s="27"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
@@ -3280,42 +3327,42 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">박</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="E9" s="27"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3323,38 +3370,38 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C10" s="28"/>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">멍</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">ㄴ</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -3362,43 +3409,43 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 姑</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">혜</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="26"/>
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">개야</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3406,36 +3453,36 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="27"/>
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 △</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="27"/>
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 姑</t>
         </is>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="27"/>
+      <c r="H12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 姑</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -3443,38 +3490,38 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="27"/>
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="27"/>
+      <c r="H13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3482,32 +3529,32 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E14" s="28"/>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="28"/>
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -3515,35 +3562,35 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="26"/>
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E15" s="26"/>
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="G15" s="26"/>
+      <c r="H15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
 姑</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">검</t>
         </is>
@@ -3551,33 +3598,33 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="27"/>
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="27"/>
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="27"/>
+      <c r="H16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
@@ -3585,34 +3632,34 @@
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="27"/>
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="E17" s="27"/>
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="27"/>
+      <c r="H17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3620,30 +3667,30 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E18" s="28"/>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="G18" s="28"/>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I18" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>

--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -3051,20 +3051,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="25" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="25" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="25" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="25" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="25" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="25" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="25" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="25" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="25" t="inlineStr">
         <is>

--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -3110,7 +3110,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">가강</t>
+          <t xml:space="preserve">가
+강</t>
         </is>
       </c>
       <c r="H3" s="25" t="inlineStr">
@@ -3194,7 +3195,8 @@
       </c>
       <c r="G5" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">만살</t>
+          <t xml:space="preserve">만
+살</t>
         </is>
       </c>
       <c r="H5" s="25" t="inlineStr">
@@ -3275,7 +3277,10 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">깨그려오</t>
+          <t xml:space="preserve">깨
+그
+려
+오</t>
         </is>
       </c>
       <c r="H7" s="25" t="inlineStr">
@@ -3436,7 +3441,8 @@
       </c>
       <c r="G11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">개야</t>
+          <t xml:space="preserve">개
+야</t>
         </is>
       </c>
       <c r="H11" s="25" t="inlineStr">

--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,6 +247,27 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3088,7 +3114,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
@@ -3098,7 +3124,7 @@
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">멍</t>
         </is>
@@ -3108,7 +3134,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 강</t>
@@ -3119,7 +3145,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="26" t="inlineStr">
+      <c r="I3" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3133,7 +3159,7 @@
 仲</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -3144,7 +3170,7 @@
 無</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">멍</t>
         </is>
@@ -3155,7 +3181,7 @@
 仲</t>
         </is>
       </c>
-      <c r="G4" s="27" t="inlineStr">
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">임</t>
         </is>
@@ -3166,7 +3192,7 @@
 仲</t>
         </is>
       </c>
-      <c r="I4" s="27" t="inlineStr">
+      <c r="I4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -3180,20 +3206,20 @@
 姑</t>
         </is>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="34"/>
       <c r="D5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="34"/>
       <c r="F5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">만
 살</t>
@@ -3205,7 +3231,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3218,7 +3244,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">초</t>
         </is>
@@ -3230,19 +3256,19 @@
 仲</t>
         </is>
       </c>
-      <c r="E6" s="29"/>
+      <c r="E6" s="36"/>
       <c r="F6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G6" s="28"/>
+      <c r="G6" s="35"/>
       <c r="H6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -3256,7 +3282,7 @@
 無</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
@@ -3268,14 +3294,14 @@
 潢</t>
         </is>
       </c>
-      <c r="E7" s="26"/>
+      <c r="E7" s="33"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">깨
 그
@@ -3289,7 +3315,7 @@
 無</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">검</t>
         </is>
@@ -3304,7 +3330,7 @@
 仲</t>
         </is>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="34"/>
       <c r="D8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
@@ -3312,19 +3338,19 @@
 姑</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="I8" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
@@ -3338,7 +3364,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">박</t>
         </is>
@@ -3349,14 +3375,14 @@
 仲</t>
         </is>
       </c>
-      <c r="E9" s="27"/>
+      <c r="E9" s="34"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="G9" s="30" t="inlineStr">
+      <c r="G9" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
@@ -3367,7 +3393,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I9" s="27" t="inlineStr">
+      <c r="I9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3380,13 +3406,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C10" s="28"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">멍</t>
         </is>
@@ -3396,7 +3422,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
+      <c r="G10" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">ㄴ</t>
         </is>
@@ -3406,7 +3432,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="28" t="inlineStr">
+      <c r="I10" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -3421,7 +3447,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">혜</t>
         </is>
@@ -3432,14 +3458,14 @@
 無</t>
         </is>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="33"/>
       <c r="F11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">개
 야</t>
@@ -3451,7 +3477,7 @@
 無</t>
         </is>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3465,14 +3491,14 @@
 仲</t>
         </is>
       </c>
-      <c r="C12" s="27"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 △</t>
         </is>
       </c>
-      <c r="E12" s="27"/>
+      <c r="E12" s="34"/>
       <c r="F12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
@@ -3480,7 +3506,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
@@ -3488,7 +3514,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="I12" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -3502,7 +3528,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C13" s="27" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3513,21 +3539,21 @@
 姑</t>
         </is>
       </c>
-      <c r="E13" s="27"/>
+      <c r="E13" s="34"/>
       <c r="F13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G13" s="27"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="I13" s="27" t="inlineStr">
+      <c r="I13" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3540,27 +3566,27 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="28"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="35"/>
       <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="G14" s="28"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
@@ -3574,21 +3600,21 @@
 無</t>
         </is>
       </c>
-      <c r="C15" s="26"/>
+      <c r="C15" s="33"/>
       <c r="D15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="E15" s="26"/>
+      <c r="E15" s="33"/>
       <c r="F15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G15" s="26"/>
+      <c r="G15" s="33"/>
       <c r="H15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
@@ -3596,7 +3622,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">검</t>
         </is>
@@ -3610,27 +3636,27 @@
 仲</t>
         </is>
       </c>
-      <c r="C16" s="27"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E16" s="27"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G16" s="27"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="I16" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
@@ -3644,28 +3670,28 @@
 姑</t>
         </is>
       </c>
-      <c r="C17" s="27"/>
+      <c r="C17" s="34"/>
       <c r="D17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="E17" s="27"/>
+      <c r="E17" s="34"/>
       <c r="F17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="G17" s="27"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="I17" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
@@ -3678,25 +3704,25 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="28"/>
+      <c r="C18" s="35"/>
       <c r="D18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E18" s="28"/>
+      <c r="E18" s="35"/>
       <c r="F18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="28"/>
+      <c r="G18" s="35"/>
       <c r="H18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="28" t="inlineStr">
+      <c r="I18" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>

--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,55 +212,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -366,7 +331,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
     </row>
@@ -378,7 +343,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
@@ -390,7 +355,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -402,7 +367,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">중</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
@@ -412,11 +377,7 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">팔레트 외 글자 1</t>
-        </is>
-      </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -442,7 +403,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손채보 16정간(굵은 선 4칸마다) → 4/4·16. 제목 "통영 개타령", 머리에 "&lt;잦은모리&gt; (F# key)". 오른쪽에 지운(크게 X) 1줄 초안(潢|無|仲 … 南|姑, 가사 "州?/야/개")이 있어 본 데이터에서 제외. 멜로디 율명 줄(세로 열) 4개를 줄1~4로 적음(오른쪽=1). 열과 열 사이 여백에 세로로 쓴 가사·의성어("개야 개야", "멍 멍 멍", "지지즈까라", "청사초", "불박혜라" 등)는 해당 멜로디 줄의 가사로 가장 가깝게 배치. 글씨가 겹치고 흐려 일부 율명·가사 불확실. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 가로선 4칸마다) → 4/4·16. 머리 "통영 개타령 &lt;잦은모리&gt; (F# key)". 맨 오른쪽 1줄(潢/無–仲/南/南, 가사 개야개)은 크게 X로 지운 초안이라 제외, 그 왼쪽 빈 칸 다음 줄부터 줄1. 왼쪽 빈 줄 제외 4줄. 가사는 각 율명 줄 바로 오른쪽 칸. 가사 칸의 쉼표·ㅣ 표시는 생략. 한 곡.</t>
         </is>
       </c>
     </row>
@@ -669,13 +630,13 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|仲</t>
+          <t xml:space="preserve">無|–仲</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-仲</t>
+–仲</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -709,18 +670,18 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">南|–南</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-姑</t>
+–南</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">개</t>
+          <t xml:space="preserve">개야</t>
         </is>
       </c>
       <c r="J4" s="4"/>
@@ -749,19 +710,16 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I5" s="2"/>
       <c r="J5" s="4"/>
       <c r="K5" s="2"/>
     </row>
@@ -786,23 +744,27 @@
       <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검</t>
-        </is>
-      </c>
-      <c r="J6" s="4"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">／潢|–無</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">／潢
+–無</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검둥</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢 앞 작은 사선</t>
+        </is>
+      </c>
       <c r="K6" s="2"/>
     </row>
     <row r="7">
@@ -828,22 +790,19 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">두</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+無</t>
+        </is>
+      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲 위에 지운 획</t>
+          <t xml:space="preserve">無 덧써 진함, 亻無(㒇)?</t>
         </is>
       </c>
       <c r="K7" s="2"/>
@@ -871,18 +830,18 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">南|–南</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-姑</t>
+–南</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">개</t>
+          <t xml:space="preserve">개야</t>
         </is>
       </c>
       <c r="J8" s="4"/>
@@ -911,19 +870,16 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I9" s="2"/>
       <c r="J9" s="4"/>
       <c r="K9" s="2"/>
     </row>
@@ -950,18 +906,18 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無</t>
+          <t xml:space="preserve">南|–無</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">개</t>
+          <t xml:space="preserve">개야</t>
         </is>
       </c>
       <c r="J10" s="4"/>
@@ -990,19 +946,18 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|姑</t>
+          <t xml:space="preserve">無|–無</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-無
-姑</t>
+–無</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">야</t>
+          <t xml:space="preserve">개야</t>
         </is>
       </c>
       <c r="J11" s="4"/>
@@ -1031,18 +986,18 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|仲</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-仲</t>
+          <t xml:space="preserve">無
+–南</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">개</t>
+          <t xml:space="preserve">검둥</t>
         </is>
       </c>
       <c r="J12" s="4"/>
@@ -1071,18 +1026,18 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無</t>
+          <t xml:space="preserve">仲|–仲</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-無</t>
+          <t xml:space="preserve">仲
+–仲</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">야</t>
+          <t xml:space="preserve">개야</t>
         </is>
       </c>
       <c r="J13" s="4"/>
@@ -1111,19 +1066,18 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|姑</t>
+          <t xml:space="preserve">南|–無</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-無
-姑</t>
+          <t xml:space="preserve">南
+–無</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검</t>
+          <t xml:space="preserve">개야</t>
         </is>
       </c>
       <c r="J14" s="4"/>
@@ -1152,18 +1106,18 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|仲</t>
+          <t xml:space="preserve">無|–無</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-仲</t>
+          <t xml:space="preserve">無
+–無</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">두</t>
+          <t xml:space="preserve">개야</t>
         </is>
       </c>
       <c r="J15" s="4"/>
@@ -1192,18 +1146,18 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-姑</t>
+          <t xml:space="preserve">無
+–南</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">개</t>
+          <t xml:space="preserve">검둥</t>
         </is>
       </c>
       <c r="J16" s="4"/>
@@ -1232,17 +1186,18 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">仲|–仲</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">仲
+–仲</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">야</t>
+          <t xml:space="preserve">개야</t>
         </is>
       </c>
       <c r="J17" s="4"/>
@@ -1271,22 +1226,23 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑
+–</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">가강</t>
+          <t xml:space="preserve">가랑</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">둘째 글자 강? 여백 세로 가사</t>
+          <t xml:space="preserve">姑 위에 덧쓴 획(㴌?)</t>
         </is>
       </c>
       <c r="K18" s="2"/>
@@ -1312,23 +1268,27 @@
       <c r="F19" s="2">
         <v>1</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無|仲</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-仲</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임</t>
-        </is>
-      </c>
-      <c r="J19" s="4"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|–姑</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–姑</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">입만</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 입(잎)</t>
+        </is>
+      </c>
       <c r="K19" s="2"/>
     </row>
     <row r="20">
@@ -1354,18 +1314,18 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">姑|–㴌</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-姑</t>
+          <t xml:space="preserve">姑
+–㴌</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">만살</t>
+          <t xml:space="preserve">살짝</t>
         </is>
       </c>
       <c r="J20" s="4"/>
@@ -1394,15 +1354,20 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I21" s="2"/>
+          <t xml:space="preserve">潢
+–無</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해도</t>
+        </is>
+      </c>
       <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
@@ -1427,27 +1392,24 @@
       <c r="F22" s="2">
         <v>2</v>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">깨그려오</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흐려 불확실</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無|南</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짖</t>
+        </is>
+      </c>
+      <c r="J22" s="4"/>
       <c r="K22" s="2"/>
     </row>
     <row r="23">
@@ -1471,18 +1433,27 @@
       <c r="F23" s="2">
         <v>2</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="4"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|仲</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+仲</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑 앞 획(亻?)</t>
+        </is>
+      </c>
       <c r="K23" s="2"/>
     </row>
     <row r="24">
@@ -1506,27 +1477,23 @@
       <c r="F24" s="2">
         <v>2</v>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|姑</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|–南</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">것</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첫 글자 것/겄?</t>
-        </is>
-      </c>
+–南</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개야</t>
+        </is>
+      </c>
+      <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
     <row r="25">
@@ -1552,19 +1519,17 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㄴ</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+–
+△</t>
+        </is>
+      </c>
+      <c r="I25" s="2"/>
       <c r="J25" s="4"/>
       <c r="K25" s="2"/>
     </row>
@@ -1591,18 +1556,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-無</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">개야</t>
+          <t xml:space="preserve">청</t>
         </is>
       </c>
       <c r="J26" s="4"/>
@@ -1631,17 +1595,20 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|姑</t>
+          <t xml:space="preserve">㴌|–無</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-無
-姑</t>
-        </is>
-      </c>
-      <c r="I27" s="2"/>
+          <t xml:space="preserve">㴌
+–無</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
       <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
@@ -1668,16 +1635,20 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|仲</t>
+          <t xml:space="preserve">㴌|–㴌</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-仲</t>
-        </is>
-      </c>
-      <c r="I28" s="2"/>
+          <t xml:space="preserve">㴌
+–㴌</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초롱</t>
+        </is>
+      </c>
       <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
@@ -1704,13 +1675,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-無</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I29" s="2"/>
@@ -1740,16 +1711,19 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-姑</t>
-        </is>
-      </c>
-      <c r="I30" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">불</t>
+        </is>
+      </c>
       <c r="J30" s="4"/>
       <c r="K30" s="2"/>
     </row>
@@ -1776,15 +1750,20 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㴌|–無</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I31" s="2"/>
+          <t xml:space="preserve">㴌
+–無</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밝</t>
+        </is>
+      </c>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
@@ -1811,16 +1790,20 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">㴌|–㴌</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="I32" s="2"/>
+          <t xml:space="preserve">㴌
+–㴌</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">혀라</t>
+        </is>
+      </c>
       <c r="J32" s="4"/>
       <c r="K32" s="2"/>
     </row>
@@ -1834,29 +1817,38 @@
         </is>
       </c>
       <c r="C33" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2">
-        <v>4</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|–</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌 왼쪽 위 작은 글자(㳞?)</t>
+        </is>
+      </c>
       <c r="K33" s="2"/>
     </row>
     <row r="34">
@@ -1875,36 +1867,33 @@
         <v>3</v>
       </c>
       <c r="E34" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2">
         <v>1</v>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">멍</t>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|湳</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님만</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">州처럼 보이나 팔레트 밖, 모양 불확실</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+          <t xml:space="preserve">湳 둘레 동그라미 표시</t>
+        </is>
+      </c>
+      <c r="K34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
@@ -1922,28 +1911,32 @@
         <v>3</v>
       </c>
       <c r="E35" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="2">
         <v>1</v>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|無</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">멍</t>
-        </is>
-      </c>
-      <c r="J35" s="4"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳|–仲</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+–仲</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">와거</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳 덧써 진함; 가사 와/오?</t>
+        </is>
+      </c>
       <c r="K35" s="2"/>
     </row>
     <row r="36">
@@ -1962,22 +1955,27 @@
         <v>3</v>
       </c>
       <c r="E36" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="2">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㴌|△</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I36" s="2"/>
+          <t xml:space="preserve">㴌
+△</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">든</t>
+        </is>
+      </c>
       <c r="J36" s="4"/>
       <c r="K36" s="2"/>
     </row>
@@ -1997,29 +1995,28 @@
         <v>3</v>
       </c>
       <c r="E37" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="2">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|㴌|仲</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-㴌
-仲</t>
-        </is>
-      </c>
-      <c r="I37" s="3"/>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌 겹쳐 적힘 불확실</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|–潢</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–潢</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개야</t>
+        </is>
+      </c>
+      <c r="J37" s="4"/>
       <c r="K37" s="2"/>
     </row>
     <row r="38">
@@ -2038,24 +2035,27 @@
         <v>3</v>
       </c>
       <c r="E38" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38" s="2">
         <v>2</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無|潢</t>
+          <t xml:space="preserve">潢|–潢</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無
-潢</t>
-        </is>
-      </c>
-      <c r="I38" s="2"/>
+–潢</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개야</t>
+        </is>
+      </c>
       <c r="J38" s="4"/>
       <c r="K38" s="2"/>
     </row>
@@ -2075,24 +2075,28 @@
         <v>3</v>
       </c>
       <c r="E39" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F39" s="2">
         <v>2</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無|姑</t>
+          <t xml:space="preserve">南|無|南</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">南
 無
-姑</t>
-        </is>
-      </c>
-      <c r="I39" s="2"/>
+南</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검둥</t>
+        </is>
+      </c>
       <c r="J39" s="4"/>
       <c r="K39" s="2"/>
     </row>
@@ -2112,23 +2116,27 @@
         <v>3</v>
       </c>
       <c r="E40" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F40" s="2">
         <v>2</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|仲</t>
+          <t xml:space="preserve">仲|–仲</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-仲</t>
-        </is>
-      </c>
-      <c r="I40" s="2"/>
+–仲</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개야</t>
+        </is>
+      </c>
       <c r="J40" s="4"/>
       <c r="K40" s="2"/>
     </row>
@@ -2148,24 +2156,25 @@
         <v>3</v>
       </c>
       <c r="E41" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F41" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">無|–潢</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">無
+–潢</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">멍</t>
+          <t xml:space="preserve">개야</t>
         </is>
       </c>
       <c r="J41" s="4"/>
@@ -2187,23 +2196,27 @@
         <v>3</v>
       </c>
       <c r="E42" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F42" s="2">
         <v>3</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無</t>
+          <t xml:space="preserve">潢|–潢</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="I42" s="2"/>
+          <t xml:space="preserve">潢
+–潢</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개야</t>
+        </is>
+      </c>
       <c r="J42" s="4"/>
       <c r="K42" s="2"/>
     </row>
@@ -2223,23 +2236,28 @@
         <v>3</v>
       </c>
       <c r="E43" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43" s="2">
         <v>3</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|△</t>
+          <t xml:space="preserve">南|無|南</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-△</t>
-        </is>
-      </c>
-      <c r="I43" s="2"/>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검둥</t>
+        </is>
+      </c>
       <c r="J43" s="4"/>
       <c r="K43" s="2"/>
     </row>
@@ -2259,23 +2277,27 @@
         <v>3</v>
       </c>
       <c r="E44" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F44" s="2">
         <v>3</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">仲|–仲</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="I44" s="2"/>
+          <t xml:space="preserve">仲
+–仲</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개야</t>
+        </is>
+      </c>
       <c r="J44" s="4"/>
       <c r="K44" s="2"/>
     </row>
@@ -2295,22 +2317,28 @@
         <v>3</v>
       </c>
       <c r="E45" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F45" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">南|無|南</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I45" s="2"/>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짖</t>
+        </is>
+      </c>
       <c r="J45" s="4"/>
       <c r="K45" s="2"/>
     </row>
@@ -2330,23 +2358,27 @@
         <v>3</v>
       </c>
       <c r="E46" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F46" s="2">
         <v>4</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無</t>
+          <t xml:space="preserve">姑|–仲</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="I46" s="2"/>
+          <t xml:space="preserve">姑
+–仲</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지를마</t>
+        </is>
+      </c>
       <c r="J46" s="4"/>
       <c r="K46" s="2"/>
     </row>
@@ -2366,23 +2398,27 @@
         <v>3</v>
       </c>
       <c r="E47" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F47" s="2">
         <v>4</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|仲</t>
+          <t xml:space="preserve">南|–南</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="I47" s="2"/>
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
       <c r="J47" s="4"/>
       <c r="K47" s="2"/>
     </row>
@@ -2402,20 +2438,20 @@
         <v>3</v>
       </c>
       <c r="E48" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F48" s="2">
         <v>4</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-姑</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2432,28 +2468,34 @@
         </is>
       </c>
       <c r="C49" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F49" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">南|無|南</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I49" s="2"/>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짖</t>
+        </is>
+      </c>
       <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
@@ -2473,33 +2515,28 @@
         <v>4</v>
       </c>
       <c r="E50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="2">
         <v>1</v>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|無|姑</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無
-姑</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">여백 "청사초3-1" 세로 가사</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|–仲</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–仲</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지를</t>
+        </is>
+      </c>
+      <c r="J50" s="4"/>
       <c r="K50" s="2"/>
     </row>
     <row r="51">
@@ -2518,25 +2555,25 @@
         <v>4</v>
       </c>
       <c r="E51" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="2">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|仲</t>
+          <t xml:space="preserve">南|–南</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-仲</t>
+          <t xml:space="preserve">南
+–南</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">마라</t>
         </is>
       </c>
       <c r="J51" s="4"/>
@@ -2558,20 +2595,21 @@
         <v>4</v>
       </c>
       <c r="E52" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" s="2">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-姑</t>
+          <t xml:space="preserve">–
+–
+△</t>
         </is>
       </c>
       <c r="I52" s="2"/>
@@ -2594,24 +2632,25 @@
         <v>4</v>
       </c>
       <c r="E53" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">姑|–㴌</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">姑
+–㴌</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">초</t>
+          <t xml:space="preserve">멍멍</t>
         </is>
       </c>
       <c r="J53" s="4"/>
@@ -2633,32 +2672,25 @@
         <v>4</v>
       </c>
       <c r="E54" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F54" s="2">
         <v>2</v>
       </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|無</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">불</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"불박혜라" 여백 가사</t>
-        </is>
-      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|–|△</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–
+△</t>
+        </is>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="4"/>
       <c r="K54" s="2"/>
     </row>
     <row r="55">
@@ -2677,24 +2709,27 @@
         <v>4</v>
       </c>
       <c r="E55" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F55" s="2">
         <v>2</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑|仲</t>
+          <t xml:space="preserve">姑|–㴌</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-姑
-仲</t>
-        </is>
-      </c>
-      <c r="I55" s="2"/>
+–㴌</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">멍멍</t>
+        </is>
+      </c>
       <c r="J55" s="4"/>
       <c r="K55" s="2"/>
     </row>
@@ -2714,27 +2749,24 @@
         <v>4</v>
       </c>
       <c r="E56" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" s="2">
         <v>2</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">–|–|△</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+–
+△</t>
+        </is>
+      </c>
+      <c r="I56" s="2"/>
       <c r="J56" s="4"/>
       <c r="K56" s="2"/>
     </row>
@@ -2754,22 +2786,28 @@
         <v>4</v>
       </c>
       <c r="E57" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">南|無|南</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I57" s="2"/>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짖</t>
+        </is>
+      </c>
       <c r="J57" s="4"/>
       <c r="K57" s="2"/>
     </row>
@@ -2789,139 +2827,145 @@
         <v>4</v>
       </c>
       <c r="E58" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F58" s="2">
         <v>3</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無|姑</t>
+          <t xml:space="preserve">姑|–仲</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–仲</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지를</t>
+        </is>
+      </c>
+      <c r="J58" s="4"/>
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>1</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
+        </is>
+      </c>
+      <c r="C59" s="2">
+        <v>4</v>
+      </c>
+      <c r="D59" s="2">
+        <v>4</v>
+      </c>
+      <c r="E59" s="2">
+        <v>11</v>
+      </c>
+      <c r="F59" s="2">
+        <v>3</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|–南</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마라</t>
+        </is>
+      </c>
+      <c r="J59" s="4"/>
+      <c r="K59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>1</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
+        </is>
+      </c>
+      <c r="C60" s="2">
+        <v>4</v>
+      </c>
+      <c r="D60" s="2">
+        <v>4</v>
+      </c>
+      <c r="E60" s="2">
+        <v>12</v>
+      </c>
+      <c r="F60" s="2">
+        <v>3</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|–|△</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–
+△</t>
+        </is>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>1</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
+        </is>
+      </c>
+      <c r="C61" s="2">
+        <v>4</v>
+      </c>
+      <c r="D61" s="2">
+        <v>4</v>
+      </c>
+      <c r="E61" s="2">
+        <v>13</v>
+      </c>
+      <c r="F61" s="2">
+        <v>4</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無|南</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
-姑</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">혜</t>
-        </is>
-      </c>
-      <c r="J58" s="4"/>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2">
-        <v>1</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
-        </is>
-      </c>
-      <c r="C59" s="2">
-        <v>4</v>
-      </c>
-      <c r="D59" s="2">
-        <v>4</v>
-      </c>
-      <c r="E59" s="2">
-        <v>10</v>
-      </c>
-      <c r="F59" s="2">
-        <v>3</v>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|仲</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2">
-        <v>1</v>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
-        </is>
-      </c>
-      <c r="C60" s="2">
-        <v>4</v>
-      </c>
-      <c r="D60" s="2">
-        <v>4</v>
-      </c>
-      <c r="E60" s="2">
-        <v>11</v>
-      </c>
-      <c r="F60" s="2">
-        <v>3</v>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|姑</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라</t>
-        </is>
-      </c>
-      <c r="J60" s="4"/>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2">
-        <v>1</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
-        </is>
-      </c>
-      <c r="C61" s="2">
-        <v>4</v>
-      </c>
-      <c r="D61" s="2">
-        <v>4</v>
-      </c>
-      <c r="E61" s="2">
-        <v>12</v>
-      </c>
-      <c r="F61" s="2">
-        <v>3</v>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I61" s="2"/>
+南</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
       <c r="J61" s="4"/>
       <c r="K61" s="2"/>
     </row>
@@ -2941,23 +2985,27 @@
         <v>4</v>
       </c>
       <c r="E62" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" s="2">
         <v>4</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無</t>
+          <t xml:space="preserve">姑|–仲</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="I62" s="2"/>
+          <t xml:space="preserve">姑
+–仲</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지를마</t>
+        </is>
+      </c>
       <c r="J62" s="4"/>
       <c r="K62" s="2"/>
     </row>
@@ -2977,24 +3025,32 @@
         <v>4</v>
       </c>
       <c r="E63" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F63" s="2">
         <v>4</v>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|仲</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="I63" s="2"/>
-      <c r="J63" s="4"/>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|–南</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 게?</t>
+        </is>
+      </c>
       <c r="K63" s="2"/>
     </row>
     <row r="64">
@@ -3013,63 +3069,28 @@
         <v>4</v>
       </c>
       <c r="E64" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F64" s="2">
         <v>4</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-姑</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I64" s="2"/>
       <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65">
-      <c r="A65" s="2">
-        <v>1</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
-        </is>
-      </c>
-      <c r="C65" s="2">
-        <v>4</v>
-      </c>
-      <c r="D65" s="2">
-        <v>4</v>
-      </c>
-      <c r="E65" s="2">
-        <v>16</v>
-      </c>
-      <c r="F65" s="2">
-        <v>4</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I65" s="2"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K65"/>
+  <autoFilter ref="A1:K64"/>
 </worksheet>
 </file>
 
@@ -3090,7 +3111,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="82.06" customHeight="1">
+    <row r="2" ht="77.61" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3105,626 +3126,750 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="82.06" customHeight="1">
+    <row r="3" ht="77.61" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
-姑</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청</t>
+南</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짖</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="E3" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">멍</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
+          <t xml:space="preserve">㴌
+–</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우
+리</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가
+랑</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가
-강</t>
-        </is>
-      </c>
-      <c r="H3" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I3" s="33" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="82.06" customHeight="1">
+    <row r="4" ht="77.61" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–仲</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지
+를</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+湳</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님
+만</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–姑</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">입
+만</t>
+        </is>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–仲</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="77.61" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마
+라</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+–仲</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">와
+거</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–㴌</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">살
+짝</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="77.61" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–
+△</t>
+        </is>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+△</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">든</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–無</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해
+도</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I6" s="27"/>
+    </row>
+    <row r="7" ht="77.61" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–㴌</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">멍
+멍</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–潢</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짖</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">／潢
+–無</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검
+둥</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="77.61" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–
+△</t>
+        </is>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–潢</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">멍</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-仲</t>
-        </is>
-      </c>
-      <c r="G4" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-仲</t>
-        </is>
-      </c>
-      <c r="I4" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="82.06" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="G5" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">만
-살</t>
-        </is>
-      </c>
-      <c r="H5" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="I5" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="82.06" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C6" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">초</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-㴌
-仲</t>
-        </is>
-      </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I6" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="82.06" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">불</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無
-潢</t>
-        </is>
-      </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">깨
-그
-려
-오</t>
-        </is>
-      </c>
-      <c r="H7" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I7" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="82.06" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="I8" s="26"/>
+    </row>
+    <row r="9" ht="77.61" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-姑
-仲</t>
-        </is>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無
-姑</t>
-        </is>
-      </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I8" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">두</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="82.06" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-仲</t>
-        </is>
-      </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">것</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="I9" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="82.06" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E10" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">멍</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G10" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㄴ</t>
-        </is>
-      </c>
-      <c r="H10" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I10" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="82.06" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="25" t="inlineStr">
+–㴌</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">멍
+멍</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
-姑</t>
-        </is>
-      </c>
-      <c r="C11" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">혜</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
+南</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검
+둥</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="G11" s="33" t="inlineStr">
+–南</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">개
 야</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="I11" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="82.06" customHeight="1">
+–南</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="77.61" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–
+△</t>
+        </is>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+–仲</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–
+△</t>
+        </is>
+      </c>
+      <c r="G10" s="27"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I10" s="27"/>
+    </row>
+    <row r="11" ht="77.61" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짖</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–潢</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–無</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="77.61" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="25" t="inlineStr">
+–仲</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지
+를</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
+–潢</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–無</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–無</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="77.61" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마
+라</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검
+둥</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–㴌</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초
+롱</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–南</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검
+둥</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="77.61" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–
 △</t>
         </is>
       </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+–仲</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+–仲</t>
+        </is>
+      </c>
+      <c r="I14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="77.61" customHeight="1">
+      <c r="A15" s="0"/>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짖</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">불</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–無</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="77.61" customHeight="1">
+      <c r="A16" s="0"/>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–仲</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지
+를
+마</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–仲</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지
+를
+마</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–無</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밝</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-無
-姑</t>
-        </is>
-      </c>
-      <c r="G12" s="34"/>
-      <c r="H12" s="25" t="inlineStr">
+–無</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="77.61" customHeight="1">
+      <c r="A17" s="0"/>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–㴌</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">혀
+라</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-無
-姑</t>
-        </is>
-      </c>
-      <c r="I12" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="82.06" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="25" t="inlineStr">
+–南</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검
+둥</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="77.61" customHeight="1">
+      <c r="A18" s="0"/>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C18" s="27"/>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="E18" s="27"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-仲</t>
-        </is>
-      </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-仲</t>
-        </is>
-      </c>
-      <c r="I13" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="82.06" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E14" s="35"/>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="I14" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="82.06" customHeight="1">
-      <c r="A15" s="0"/>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-姑</t>
-        </is>
-      </c>
-      <c r="G15" s="33"/>
-      <c r="H15" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-無
-姑</t>
-        </is>
-      </c>
-      <c r="I15" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="82.06" customHeight="1">
-      <c r="A16" s="0"/>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-仲</t>
-        </is>
-      </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-仲</t>
-        </is>
-      </c>
-      <c r="I16" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">두</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="82.06" customHeight="1">
-      <c r="A17" s="0"/>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="I17" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="82.06" customHeight="1">
-      <c r="A18" s="0"/>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E18" s="35"/>
-      <c r="F18" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="G18" s="35"/>
-      <c r="H18" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I18" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
+–仲</t>
+        </is>
+      </c>
+      <c r="I18" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개
+야</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -403,7 +403,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 가로선 4칸마다) → 4/4·16. 머리 "통영 개타령 &lt;잦은모리&gt; (F# key)". 맨 오른쪽 1줄(潢/無–仲/南/南, 가사 개야개)은 크게 X로 지운 초안이라 제외, 그 왼쪽 빈 칸 다음 줄부터 줄1. 왼쪽 빈 줄 제외 4줄. 가사는 각 율명 줄 바로 오른쪽 칸. 가사 칸의 쉼표·ㅣ 표시는 생략. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 가로선 4칸마다) → 4/4·16. 머리 "통영 개타령 &lt;잦은모리&gt; (F# key)". 맨 오른쪽 1줄(潢/無–仲/南/南, 가사 개야개)은 크게 X로 지운 초안이라 제외, 그 왼쪽 빈 칸 다음 줄부터 줄1. 왼쪽 빈 줄 제외 4줄. 가사는 각 율명 줄 바로 오른쪽 칸. 가사 칸의 쉼표·ㅣ 표시는 생략. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳 덧써 진함; 가사 와/오?</t>
+          <t xml:space="preserve">湳 덧써 진함; 가사 와/오?; 仲/㳞?</t>
         </is>
       </c>
       <c r="K35" s="2"/>

--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -781,10 +781,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -463,34 +463,9 @@
 리</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">姑
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+    <t xml:space="preserve">姑
+姑
+–</t>
   </si>
   <si>
     <t xml:space="preserve">가
@@ -506,34 +481,9 @@
 를</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">湳</t>
-    </r>
+    <t xml:space="preserve">㴌
+–
+湳</t>
   </si>
   <si>
     <t xml:space="preserve">님
@@ -585,34 +535,9 @@
 야</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">△</t>
-    </r>
+    <t xml:space="preserve">㴌
+–
+△</t>
   </si>
   <si>
     <t xml:space="preserve">潢
@@ -642,25 +567,9 @@
 潢</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑
+    <t xml:space="preserve">姑
 仲
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+南</t>
   </si>
   <si>
     <t xml:space="preserve">仲
@@ -722,17 +631,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -854,7 +763,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -908,6 +817,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3321,422 +3270,422 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I18"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="81.63" customHeight="true">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B3" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B4" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="21" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B5" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="21" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B6" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="23"/>
+      <c r="D6" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I6" s="13"/>
-    </row>
-    <row r="7" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="I6" s="23"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B7" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B8" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="21"/>
+      <c r="D8" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="12"/>
-    </row>
-    <row r="9" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="I8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B9" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="21" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="23"/>
+      <c r="D10" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="23"/>
+      <c r="H10" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="13"/>
-    </row>
-    <row r="11" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="I10" s="23"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B11" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="18" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B12" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="21" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B13" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B14" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="23" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B15" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="18" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B16" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="21" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="9" t="s">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B17" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="91.25" customHeight="true">
+      <c r="B18" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="23"/>
+      <c r="D18" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="7" t="s">
+      <c r="E18" s="23"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="23" t="s">
         <v>151</v>
       </c>
     </row>
@@ -3746,7 +3695,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="77" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/통영 개타령.xlsx
+++ b/sheets/민요/검수/통영 개타령.xlsx
@@ -3276,13 +3276,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
   </cols>
   <sheetData>
